--- a/ADS_POO.xlsx
+++ b/ADS_POO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\PycharmProjects\ProjetoEnadeUnip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB571F7-7587-4FF8-A54A-08BF6199345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67484C0D-E740-4258-9CFA-8CDB9581BA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2F9E6124-CF93-42DC-A7D1-63D7C1D2D28E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
   <si>
     <t>TOMO</t>
   </si>
@@ -770,6 +770,20 @@
 JUSTIFICATIVAS.
 O item I a afirmativa está correta, pois as variáveis com acesso private somente são acessíveis a métodos da classe em que são declarados. É a definição de variáveis privadas.
 O item IV a afirmativa está correta, pois o polimorfismo elimina a necessidade de múltiplos comandos condicionais, como o switch, permitindo que chamadas de métodos sejam resolvidas de acordo com o tipo do objeto.</t>
+  </si>
+  <si>
+    <t>questao11_tomo1.jpg</t>
+  </si>
+  <si>
+    <t>questao10_tomo1.jpg</t>
+  </si>
+  <si>
+    <t>Com relação a conceitos de orientação a objetos, julgue os itens.
+I - As variáveis ou métodos declarados com modificador de acesso private só são acessíveis a métodos da classe em que são declarados.
+II - Uma classe deve possuir uma única declaração de método construtor.
+III - Uma instância de uma classe abstrata herda atributos e métodos de sua superclasse direta.
+IV - O polimorfismo permite substituir a lógica condicional múltipla (lógica switch ou faça caso).
+São corretos apenas os itens</t>
   </si>
 </sst>
 </file>
@@ -1440,6 +1454,9 @@
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
+      <c r="H7" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
@@ -1510,6 +1527,9 @@
       </c>
       <c r="F12" s="7" t="s">
         <v>30</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1615,7 +1635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="C21" s="8"/>
       <c r="D21" s="14" t="s">
         <v>5</v>
@@ -1647,7 +1667,7 @@
         <v>7</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>2</v>

--- a/ADS_POO.xlsx
+++ b/ADS_POO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\PycharmProjects\ProjetoEnadeUnip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67484C0D-E740-4258-9CFA-8CDB9581BA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAE1D47-0556-464A-8892-91A8D9D675AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2F9E6124-CF93-42DC-A7D1-63D7C1D2D28E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="104">
   <si>
     <t>TOMO</t>
   </si>
@@ -784,6 +784,9 @@
 III - Uma instância de uma classe abstrata herda atributos e métodos de sua superclasse direta.
 IV - O polimorfismo permite substituir a lógica condicional múltipla (lógica switch ou faça caso).
 São corretos apenas os itens</t>
+  </si>
+  <si>
+    <t>questao6_tomo3.jpg</t>
   </si>
 </sst>
 </file>
@@ -1583,13 +1586,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="18"/>
       <c r="D17" s="14"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:7" ht="248.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="248.4" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>2</v>
       </c>
@@ -1609,7 +1612,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="56.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="56.4" x14ac:dyDescent="0.3">
       <c r="D19" s="21" t="s">
         <v>3</v>
       </c>
@@ -1620,7 +1623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="C20" s="8"/>
       <c r="D20" s="14" t="s">
         <v>4</v>
@@ -1635,7 +1638,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="C21" s="8"/>
       <c r="D21" s="14" t="s">
         <v>5</v>
@@ -1647,7 +1650,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="C22" s="22"/>
       <c r="D22" s="26" t="s">
         <v>6</v>
@@ -1659,7 +1662,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="165.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
         <v>2</v>
       </c>
@@ -1679,7 +1682,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="69" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="69" x14ac:dyDescent="0.3">
       <c r="C24" s="22"/>
       <c r="D24" s="21" t="s">
         <v>3</v>
@@ -1691,7 +1694,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="179.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="179.4" x14ac:dyDescent="0.3">
       <c r="C25" s="22"/>
       <c r="D25" s="14" t="s">
         <v>4</v>
@@ -1706,7 +1709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C26" s="22"/>
       <c r="D26" s="14" t="s">
         <v>5</v>
@@ -1718,7 +1721,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C27" s="22"/>
       <c r="D27" s="26" t="s">
         <v>6</v>
@@ -1730,7 +1733,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="345" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="345" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>3</v>
       </c>
@@ -1752,8 +1755,11 @@
       <c r="G28" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="H28" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="C29" s="23"/>
       <c r="D29" s="14" t="s">
         <v>3</v>
@@ -1765,7 +1771,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="C30" s="24"/>
       <c r="D30" s="14" t="s">
         <v>4</v>
@@ -1777,7 +1783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="55.2" x14ac:dyDescent="0.3">
       <c r="C31" s="24"/>
       <c r="D31" s="14" t="s">
         <v>5</v>
@@ -1789,7 +1795,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="15" x14ac:dyDescent="0.3">
       <c r="C32" s="24"/>
       <c r="D32" s="14" t="s">
         <v>6</v>

--- a/ADS_POO.xlsx
+++ b/ADS_POO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro\PycharmProjects\ProjetoEnadeUnip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAE1D47-0556-464A-8892-91A8D9D675AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D75D2A4-84E2-443B-9185-2DA75BE3D633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{2F9E6124-CF93-42DC-A7D1-63D7C1D2D28E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="103">
   <si>
     <t>TOMO</t>
   </si>
@@ -728,14 +728,6 @@
   <si>
     <t>Alternativa incorreta.JUSTIFICATIVA.
 Ver justificativas das letras A e B.</t>
-  </si>
-  <si>
-    <t>Com relação a conceitos de orientação a objetos, julgue os itens.
-I.	As variáveis ou métodos declarados com modificador de acesso private só são acessíveis a métodos da classe em que são declarados.
-II.	Uma classe deve possuir uma única declaração de método construtor.
-III.	Uma instância de uma classe abstrata herda atributos e métodos de sua superclasse direta.
-IV.	O polimorfismo permite substituir a lógica condicional múltipla (lógica switch ou faça caso).
-São corretos apenas os itens</t>
   </si>
   <si>
     <t>I e II.</t>
@@ -1458,7 +1450,7 @@
         <v>22</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1532,7 +1524,7 @@
         <v>30</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1670,16 +1662,16 @@
         <v>7</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>2</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="69" x14ac:dyDescent="0.3">
@@ -1688,10 +1680,10 @@
         <v>3</v>
       </c>
       <c r="E24" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="179.4" x14ac:dyDescent="0.3">
@@ -1700,10 +1692,10 @@
         <v>4</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>16</v>
@@ -1715,10 +1707,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -1727,10 +1719,10 @@
         <v>6</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="345" x14ac:dyDescent="0.3">
@@ -1756,7 +1748,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
@@ -1946,16 +1938,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="152.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="10">
-        <v>4</v>
-      </c>
-      <c r="B43" s="10">
-        <v>7</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>89</v>
-      </c>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C43" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
